--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487543_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487543_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.341</v>
+        <v>3.2713</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0156</v>
+        <v>3.9727</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6746</v>
+        <v>-0.7014</v>
       </c>
       <c r="G2" t="n">
         <v>3.2818</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1366</v>
+        <v>-0.2063</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1059</v>
+        <v>0.0629</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2425</v>
+        <v>-0.2692</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7476</v>
+        <v>-0.7209</v>
       </c>
       <c r="E3" t="n">
         <v>-0.8224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1015</v>
       </c>
       <c r="G3" t="n">
         <v>0.2933</v>
@@ -688,13 +688,13 @@
         <v>0.1958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T3" t="n">
         <v>0.1364</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2754</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MUJICA LANDAETA</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9335</v>
+        <v>-0.9065</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5494</v>
+        <v>-1.189</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3841</v>
+        <v>0.2825</v>
       </c>
       <c r="G4" t="n">
-        <v>0.793</v>
+        <v>-1.724</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8078</v>
+        <v>-2.5023</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0148</v>
+        <v>0.7783</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9774</v>
+        <v>-1.2584</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7349</v>
+        <v>-2.0263</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2425</v>
+        <v>0.7679</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1844</v>
+        <v>-0.4656</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.476</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2573</v>
+        <v>0.0104</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5868</v>
+        <v>0.23</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4109</v>
+        <v>0.0694</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8241000000000001</v>
+        <v>0.1606</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>I. FERNANDEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2729</v>
+        <v>-1.1354</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5554</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2825</v>
+        <v>-0.525</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.724</v>
+        <v>-1.4981</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5023</v>
+        <v>2.5442</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7783</v>
+        <v>-4.0422</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2584</v>
+        <v>-0.3834</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.0263</v>
+        <v>1.6536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7679</v>
+        <v>-2.0371</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4656</v>
+        <v>-1.1146</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.476</v>
+        <v>0.8905</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0104</v>
+        <v>-2.0052</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1364</v>
+        <v>-1.5993</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.297</v>
+        <v>-0.7017</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1606</v>
+        <v>-0.8976</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4332</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MUÑOZ</t>
+          <t>A. BLANCO BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.417</v>
+        <v>-1.5536</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0791</v>
+        <v>-1.4351</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3379</v>
+        <v>-0.1184</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4981</v>
+        <v>-0.5462</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5442</v>
+        <v>-1.1572</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.0422</v>
+        <v>0.611</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3834</v>
+        <v>-0.2888</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6536</v>
+        <v>-1.026</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.0371</v>
+        <v>0.7371</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1146</v>
+        <v>-0.2573</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8905</v>
+        <v>-0.1312</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0052</v>
+        <v>-0.1261</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8809</v>
+        <v>-0.6525</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1704</v>
+        <v>-0.167</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7105</v>
+        <v>-0.4855</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1578</v>
+        <v>-0.5507</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4332</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BLANCO BLANCO</t>
+          <t>S. MUJICA LANDAETA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.755</v>
+        <v>-1.78</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9039</v>
+        <v>-1.5563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1489</v>
+        <v>-0.2237</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5462</v>
+        <v>0.793</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1572</v>
+        <v>0.8078</v>
       </c>
       <c r="I7" t="n">
-        <v>0.611</v>
+        <v>-0.0148</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2888</v>
+        <v>0.9774</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.026</v>
+        <v>0.7349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7371</v>
+        <v>0.2425</v>
       </c>
       <c r="M7" t="n">
+        <v>-0.1844</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+      <c r="O7" t="n">
         <v>-0.2573</v>
       </c>
-      <c r="N7" t="n">
-        <v>-0.1312</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-0.1261</v>
-      </c>
       <c r="P7" t="n">
-        <v>0.1958</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
         <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.854</v>
+        <v>-0.2597</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6358</v>
+        <v>0.404</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2182</v>
+        <v>-0.6637</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5507</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2028</v>
+        <v>-1.976</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3881</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5908</v>
+        <v>-2.671</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2056</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.3372</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8316</v>
+        <v>-0.5246</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2677</v>
+        <v>0.1875</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2166</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>M. SUAREZ MALLON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6529</v>
+        <v>-2.9849</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4941</v>
+        <v>-2.0345</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1587</v>
+        <v>-0.9505</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.927</v>
+        <v>-0.875</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5985</v>
+        <v>-0.2031</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3285</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5895</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6704</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0808</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3375</v>
+        <v>-0.875</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.2031</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4093</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1971</v>
+        <v>-0.11</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7993</v>
+        <v>-0.3893</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9964</v>
+        <v>0.2794</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SUAREZ MALLON</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0827</v>
+        <v>-3.474</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2392</v>
+        <v>-1.6628</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8435</v>
+        <v>-1.8112</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.875</v>
+        <v>-2.927</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2031</v>
+        <v>-0.5985</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-2.3285</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.5895</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.6704</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.875</v>
+        <v>-2.3375</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2031</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-2.4093</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2077</v>
+        <v>-1.0182</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.594</v>
+        <v>-0.3694</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3863</v>
+        <v>-0.6489</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0314</v>
+        <v>-4.607</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9804</v>
+        <v>-2.7163</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0511</v>
+        <v>-1.8907</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6332</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.911</v>
+        <v>-1.4865</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9504</v>
+        <v>-0.6864</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9605</v>
+        <v>-0.8002</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3329</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. BARREIRO BUCETA</t>
+          <t>J. HERMO ANTELO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5349</v>
+        <v>-6.1741</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5111</v>
+        <v>-4.1161</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0239</v>
+        <v>-2.058</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3836</v>
+        <v>-3.8349</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0885</v>
+        <v>-1.2528</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.2951</v>
+        <v>-2.5821</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5836</v>
+        <v>-2.6881</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.026</v>
+        <v>-0.6414</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5576</v>
+        <v>-2.0467</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8</v>
+        <v>-1.1468</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0625</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7375</v>
+        <v>-0.5354</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6433</v>
+        <v>-0.4543</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0692</v>
+        <v>-0.4488</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.0056</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8837</v>
+        <v>-1.1014</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>-1.1014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HERMO ANTELO</t>
+          <t>N. BARREIRO BUCETA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5392</v>
+        <v>-6.1939</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3208</v>
+        <v>-3.9829</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2184</v>
+        <v>-2.211</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8349</v>
+        <v>-5.3836</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2528</v>
+        <v>-1.0885</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5821</v>
+        <v>-4.2951</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.6881</v>
+        <v>-3.5836</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6414</v>
+        <v>-1.026</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0467</v>
+        <v>-2.5576</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1468</v>
+        <v>-1.8</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.0625</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5354</v>
+        <v>-1.7375</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8194</v>
+        <v>-1.3023</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6534</v>
+        <v>-0.5411</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.166</v>
+        <v>-0.7612</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1014</v>
+        <v>0.8837</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1014</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-28.8289</v>
+        <v>-28.235</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.0521</v>
+        <v>-15.458</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.7768</v>
+        <v>-12.7769</v>
       </c>
       <c r="G14" t="n">
         <v>-14.2595</v>
@@ -1531,13 +1531,13 @@
         <v>-12.3228</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9843</v>
+        <v>-0.9843000000000002</v>
       </c>
       <c r="O14" t="n">
         <v>-11.3386</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.896300000000001</v>
+        <v>-4.8963</v>
       </c>
       <c r="Q14" t="n">
         <v>-15.6676</v>
@@ -1546,13 +1546,13 @@
         <v>10.7715</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.7458</v>
+        <v>-7.151699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7493</v>
+        <v>-3.1556</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.9963</v>
+        <v>-3.996300000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.9274</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.2332</v>
+        <v>7.8147</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7949</v>
+        <v>5.5902</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4383</v>
+        <v>2.2245</v>
       </c>
       <c r="G15" t="n">
         <v>5.9854</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>1.84</v>
+        <v>1.4215</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8475</v>
+        <v>0.6428</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9925</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.159</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.1421</v>
+        <v>5.561</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0802</v>
+        <v>4.4428</v>
       </c>
       <c r="F16" t="n">
-        <v>1.062</v>
+        <v>1.1182</v>
       </c>
       <c r="G16" t="n">
         <v>2.6158</v>
@@ -1702,13 +1702,13 @@
         <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5424</v>
+        <v>1.9613</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9713</v>
+        <v>1.3339</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.6274</v>
       </c>
       <c r="V16" t="n">
         <v>1.7673</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ ALVAREZ</t>
+          <t>A. CASAIS ROMERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.015</v>
+        <v>4.9394</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4265</v>
+        <v>2.4903</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5885</v>
+        <v>2.4491</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4903</v>
+        <v>-0.2781</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1623</v>
+        <v>-1.2484</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6526</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4602</v>
+        <v>0.4313</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6414</v>
+        <v>-0.912</v>
       </c>
       <c r="L17" t="n">
-        <v>2.1016</v>
+        <v>1.3433</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0301</v>
+        <v>-0.7094</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4791</v>
+        <v>-0.3364</v>
       </c>
       <c r="O17" t="n">
-        <v>0.551</v>
+        <v>-0.373</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3917</v>
+        <v>2.7419</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3917</v>
+        <v>2.9377</v>
       </c>
       <c r="S17" t="n">
-        <v>1.133</v>
+        <v>0.9837</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9663</v>
+        <v>0.7628</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1667</v>
+        <v>0.2209</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8841</v>
+        <v>4.3092</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9712</v>
+        <v>-0.2548</v>
       </c>
       <c r="F18" t="n">
-        <v>4.8553</v>
+        <v>4.564</v>
       </c>
       <c r="G18" t="n">
         <v>2.0363</v>
@@ -1858,13 +1858,13 @@
         <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3812</v>
+        <v>0.8063</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8734</v>
+        <v>-0.157</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2546</v>
+        <v>0.9634</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8837</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CASAIS ROMERO</t>
+          <t>M. RODRIGUEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.7124</v>
+        <v>3.5125</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7739</v>
+        <v>1.7101</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9385</v>
+        <v>1.8023</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2781</v>
+        <v>2.4903</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2484</v>
+        <v>-0.1623</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9703000000000001</v>
+        <v>2.6526</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4313</v>
+        <v>1.4602</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.912</v>
+        <v>-0.6414</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3433</v>
+        <v>2.1016</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7094</v>
+        <v>1.0301</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3364</v>
+        <v>0.4791</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.373</v>
+        <v>0.551</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7419</v>
+        <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9377</v>
+        <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2434</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0465</v>
+        <v>0.25</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2898</v>
+        <v>0.3805</v>
       </c>
       <c r="V19" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>C. NOGUEROL BARRENECHEA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6451</v>
+        <v>2.6216</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5955</v>
+        <v>0.1749</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0497</v>
+        <v>2.4467</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0608</v>
+        <v>4.0676</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1364</v>
+        <v>2.9152</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0756</v>
+        <v>1.1524</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3838</v>
+        <v>4.4323</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3385</v>
+        <v>2.3663</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0452</v>
+        <v>2.066</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3229</v>
+        <v>-0.3647</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2021</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1209</v>
+        <v>-0.9136</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7834</v>
+        <v>-2.546</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>-5.0921</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1751</v>
+        <v>2.546</v>
       </c>
       <c r="S20" t="n">
-        <v>1.817</v>
+        <v>0.8247</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4029</v>
+        <v>0.5593</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4141</v>
+        <v>0.2654</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5507</v>
+        <v>0.2754</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7673</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. NOGUEROL BARRENECHEA</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4702</v>
+        <v>1.1594</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4391</v>
+        <v>0.6978</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9093</v>
+        <v>0.4616</v>
       </c>
       <c r="G21" t="n">
-        <v>4.0676</v>
+        <v>0.0608</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9152</v>
+        <v>0.1364</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1524</v>
+        <v>-0.0756</v>
       </c>
       <c r="J21" t="n">
-        <v>4.4323</v>
+        <v>0.3838</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3663</v>
+        <v>0.3385</v>
       </c>
       <c r="L21" t="n">
-        <v>2.066</v>
+        <v>0.0452</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3647</v>
+        <v>-0.3229</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5489000000000001</v>
+        <v>-0.2021</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9136</v>
+        <v>-0.1209</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.546</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.0921</v>
+        <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3267</v>
+        <v>1.3312</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0547</v>
+        <v>0.5052</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.272</v>
+        <v>0.826</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2754</v>
+        <v>0.5507</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2754</v>
+        <v>1.7673</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3684</v>
+        <v>0.6385</v>
       </c>
       <c r="E22" t="n">
         <v>-0.4369</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8053</v>
+        <v>1.0754</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2866</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0121</v>
+        <v>0.258</v>
       </c>
       <c r="T22" t="n">
         <v>0.2247</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2367</v>
+        <v>0.0334</v>
       </c>
       <c r="V22" t="n">
         <v>1.492</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8046</v>
+        <v>-0.3963</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7049</v>
+        <v>-1.0348</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0998</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.115</v>
+        <v>-0.3171</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2514</v>
+        <v>-1.2066</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1364</v>
+        <v>0.8895</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0204</v>
+        <v>-1.142</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0204</v>
+        <v>-1.3441</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.2021</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1354</v>
+        <v>0.8249</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2719</v>
+        <v>0.1375</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1364</v>
+        <v>0.6874</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0238</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0594</v>
+        <v>-0.1682</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0356</v>
+        <v>0.2469</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6659</v>
+        <v>-0.9412</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8369</v>
+        <v>-0.6488</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3418</v>
+        <v>-0.6025</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5049</v>
+        <v>-0.0463</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3171</v>
+        <v>-0.115</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2066</v>
+        <v>-0.2514</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8895</v>
+        <v>0.1364</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.142</v>
+        <v>0.0204</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.3441</v>
+        <v>0.0204</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2021</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8249</v>
+        <v>-0.1354</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1375</v>
+        <v>-0.2719</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6874</v>
+        <v>0.1364</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.362</v>
+        <v>0.132</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4752</v>
+        <v>0.0429</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1132</v>
+        <v>0.0891</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9412</v>
+        <v>-0.6659</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>28.829</v>
+        <v>29.5112</v>
       </c>
       <c r="E25" t="n">
         <v>12.7771</v>
       </c>
       <c r="F25" t="n">
-        <v>16.052</v>
+        <v>16.7341</v>
       </c>
       <c r="G25" t="n">
         <v>14.2594</v>
@@ -2395,7 +2395,7 @@
         <v>-1.1569</v>
       </c>
       <c r="P25" t="n">
-        <v>4.8963</v>
+        <v>4.896300000000002</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.7716</v>
@@ -2404,13 +2404,13 @@
         <v>15.6678</v>
       </c>
       <c r="S25" t="n">
-        <v>7.7456</v>
+        <v>8.427899999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>3.9965</v>
+        <v>3.9964</v>
       </c>
       <c r="U25" t="n">
-        <v>3.7493</v>
+        <v>4.4317</v>
       </c>
       <c r="V25" t="n">
         <v>1.9276</v>
